--- a/Employee_Reports_wi52/Levitico Jose Caniedo Q0492.xlsx
+++ b/Employee_Reports_wi52/Levitico Jose Caniedo Q0492.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -753,11 +762,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -790,11 +799,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -827,11 +836,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -864,11 +873,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -913,11 +922,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -962,11 +971,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1011,11 +1020,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1060,11 +1069,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1109,11 +1118,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1158,11 +1167,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1207,11 +1216,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1256,11 +1265,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1305,11 +1314,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1354,11 +1363,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1403,11 +1412,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1452,11 +1461,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1501,11 +1510,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1550,11 +1559,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1565,53 +1574,53 @@
       <c r="K24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Storage Retrieval Machine (AMH Trainings)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>AMH</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>LSME-AMH-M-005</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2024</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1648,11 +1657,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1697,11 +1706,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1746,11 +1755,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1795,11 +1804,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1845,11 +1854,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1894,11 +1903,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1931,11 +1940,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1980,11 +1989,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -1995,53 +2004,53 @@
       <c r="K33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-022</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>05-Apr-2025</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>05-Apr-2026</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
-        <v>-137</v>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="n">
+        <v>-145</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -2078,11 +2087,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2093,102 +2102,102 @@
       <c r="K35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-003</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>26-Jul-2025</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>26-Jul-2026</t>
         </is>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-009</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>26-Jul-2025</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>26-Jul-2026</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -2225,11 +2234,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2240,41 +2249,41 @@
       <c r="K38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Replacement of Stacker Crane Wire Rope (SOPs)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>26-Jul-2025</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>26-Jul-2026</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -2299,11 +2308,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2314,102 +2323,102 @@
       <c r="K40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-011</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2025</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2026</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-018</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2025</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2026</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="H42" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -2446,11 +2455,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2483,11 +2492,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2520,11 +2529,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2569,11 +2578,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2618,11 +2627,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2667,11 +2676,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -2704,11 +2713,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -2741,11 +2750,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -2778,11 +2787,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -2815,11 +2824,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -2852,11 +2861,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -3150,66 +3159,66 @@
       <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Climate Control Center</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>20-Oct-2025</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>66.67%</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n"/>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>3Tier Rack -G/H/A/Q51</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>04-Aug-2025</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>72.97%</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -3345,7 +3354,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3374,7 +3383,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7994</v>
+        <v>7986</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3397,7 +3406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3455,21 +3464,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ews 10 ft</t>
+          <t>stacker crane</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>24-Jul-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>18-Jun-2048</t>
+          <t>12-Jul-2048</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7973</v>
+        <v>7989</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3484,21 +3493,21 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>uld hoist</t>
+          <t>cs hoist</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>03-Aug-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>28-Jun-2048</t>
+          <t>12-Jul-2048</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7983</v>
+        <v>7989</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3513,21 +3522,21 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>turntable</t>
+          <t>h9tv</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>28-Jul-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>22-Jun-2048</t>
+          <t>12-Jul-2048</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7977</v>
+        <v>7989</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3542,21 +3551,21 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>tilting deck</t>
+          <t>ews 10 ft</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>28-Jul-2026</t>
+          <t>24-Jul-2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>22-Jun-2048</t>
+          <t>18-Jun-2048</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7977</v>
+        <v>7965</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3571,21 +3580,21 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>fmc deck</t>
+          <t>uld hoist</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>25-Jul-2026</t>
+          <t>03-Aug-2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>19-Jun-2048</t>
+          <t>28-Jun-2048</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7974</v>
+        <v>7975</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3600,21 +3609,21 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>powered roller deckmatarsop</t>
+          <t>turntable</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>24-Jul-2026</t>
+          <t>28-Jul-2026</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>18-Jun-2048</t>
+          <t>22-Jun-2048</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7973</v>
+        <v>7969</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3629,21 +3638,21 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>non powered roller deckmatarsop</t>
+          <t>tilting deck</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>25-Jul-2026</t>
+          <t>28-Jul-2026</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>19-Jun-2048</t>
+          <t>22-Jun-2048</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7974</v>
+        <v>7969</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3658,21 +3667,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ball deck</t>
+          <t>fmc deck</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>24-Jul-2026</t>
+          <t>25-Jul-2026</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>18-Jun-2048</t>
+          <t>19-Jun-2048</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7973</v>
+        <v>7966</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3687,28 +3696,173 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>24-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>18-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>7965</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>non powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>25-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>19-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7966</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>cs placing deck</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2048</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>cs input and output conveyor</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2048</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ball deck</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>24-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>18-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>7965</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>floor scale</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>25-Jul-2026</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>19-Jun-2048</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>7974</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>7966</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
